--- a/artifacts/BIST_Research_Latest.xlsx
+++ b/artifacts/BIST_Research_Latest.xlsx
@@ -49,7 +49,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ozkan Filiz'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Quality Scanner'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'RSI Scanner'!$A$1:$H$325</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Source Status'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Source Status'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">Sources!$A$1:$V$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Target Prices'!$A$1:$A$325</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Technical!$A$1:$C$325</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7536" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="533">
   <si>
     <t>Mode</t>
   </si>
@@ -1149,12 +1149,18 @@
     <t>duckdb_store</t>
   </si>
   <si>
+    <t>bist_daily_bulletin</t>
+  </si>
+  <si>
     <t>yahoo_chart</t>
   </si>
   <si>
     <t>ACTIVE</t>
   </si>
   <si>
+    <t>DEGRADED</t>
+  </si>
+  <si>
     <t>Borsa Istanbul</t>
   </si>
   <si>
@@ -1167,6 +1173,9 @@
     <t>LIVE_REFERENCE; 324 unique tickers</t>
   </si>
   <si>
+    <t>ProviderError: BIST bulletin not published for 2026-10-01</t>
+  </si>
+  <si>
     <t>provider_id</t>
   </si>
   <si>
@@ -1639,9 +1648,6 @@
   </si>
   <si>
     <t>Foreks_or_other_vendor_unverified</t>
-  </si>
-  <si>
-    <t>DEGRADED</t>
   </si>
   <si>
     <t>BLOCKED</t>
@@ -3481,7 +3487,7 @@
         <v>176</v>
       </c>
       <c r="C158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="159" spans="1:3">
@@ -12931,16 +12937,19 @@
         <v>176</v>
       </c>
       <c r="C158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D158" t="s">
-        <v>347</v>
+        <v>346</v>
+      </c>
+      <c r="E158" t="s">
+        <v>9</v>
       </c>
       <c r="F158" t="s">
         <v>348</v>
       </c>
       <c r="G158" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -18993,13 +19002,16 @@
         <v>176</v>
       </c>
       <c r="B158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C158" t="s">
-        <v>347</v>
+        <v>346</v>
+      </c>
+      <c r="D158" t="s">
+        <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -21846,7 +21858,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="12.7109375" customWidth="1"/>
@@ -21881,13 +21893,13 @@
         <v>360</v>
       </c>
       <c r="B2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -21895,13 +21907,13 @@
         <v>361</v>
       </c>
       <c r="B3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -21909,23 +21921,46 @@
         <v>362</v>
       </c>
       <c r="B4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C4" t="s">
         <v>366</v>
       </c>
+      <c r="D4" t="s">
+        <v>370</v>
+      </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E5">
         <v>324</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21960,67 +21995,67 @@
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>354</v>
@@ -22028,22 +22063,22 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -22052,10 +22087,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -22076,39 +22111,39 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="S2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="T2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="U2" s="3">
         <v>46296</v>
       </c>
       <c r="V2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F3" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -22117,16 +22152,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K3" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -22141,39 +22176,39 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S3" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="T3" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="U3" s="3">
         <v>46296</v>
       </c>
       <c r="V3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F4" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -22182,10 +22217,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K4" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -22206,54 +22241,54 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S4" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="T4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="U4" s="3">
         <v>46296</v>
       </c>
       <c r="V4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H5" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="I5" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K5" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L5" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -22271,19 +22306,19 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="T5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="U5" s="3">
         <v>46296</v>
       </c>
       <c r="V5" t="s">
-        <v>526</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -22291,19 +22326,19 @@
         <v>360</v>
       </c>
       <c r="B6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F6" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -22312,10 +22347,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K6" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -22336,39 +22371,39 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="S6" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="T6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="U6" s="3">
         <v>46296</v>
       </c>
       <c r="V6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B7" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F7" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -22377,10 +22412,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K7" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -22401,39 +22436,39 @@
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="S7" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="T7" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="U7" s="3">
         <v>46296</v>
       </c>
       <c r="V7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B8" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -22442,22 +22477,22 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -22466,39 +22501,39 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="T8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="U8" s="3">
         <v>46296</v>
       </c>
       <c r="V8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C9" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F9" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -22507,10 +22542,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K9" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -22531,36 +22566,36 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S9" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="T9" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="U9" s="3">
         <v>46296</v>
       </c>
       <c r="V9" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E10" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F10" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -22569,7 +22604,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K10" t="s">
         <v>350</v>
@@ -22593,51 +22628,51 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S10" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="U10" s="3">
         <v>46296</v>
       </c>
       <c r="V10" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B11" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="E11" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="F11" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G11" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -22649,69 +22684,69 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P11" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S11" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="T11" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="U11" s="3">
         <v>46296</v>
       </c>
       <c r="V11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B12" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E12" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="F12" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G12" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L12" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -22726,39 +22761,39 @@
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S12" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="T12" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="U12" s="3">
         <v>46296</v>
       </c>
       <c r="V12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C13" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E13" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F13" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -22767,10 +22802,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K13" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -22779,51 +22814,51 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="O13" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P13" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S13" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="T13" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="U13" s="3">
         <v>46296</v>
       </c>
       <c r="V13" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B14" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C14" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F14" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -22832,10 +22867,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="K14" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -22844,51 +22879,51 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="O14" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P14" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S14" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="T14" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="U14" s="3">
         <v>46296</v>
       </c>
       <c r="V14" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C15" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E15" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F15" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -22897,19 +22932,19 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L15" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M15" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -22918,175 +22953,175 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="T15" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="U15" s="3">
         <v>46296</v>
       </c>
       <c r="V15" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B16" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C16" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E16" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F16" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G16" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K16" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S16" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="T16" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="U16" s="3">
         <v>46296</v>
       </c>
       <c r="V16" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B17" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C17" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E17" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F17" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G17" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K17" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="P17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="S17" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="T17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="U17" s="3">
         <v>46296</v>
       </c>
       <c r="V17" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B18" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C18" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E18" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F18" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -23095,10 +23130,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="K18" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -23119,19 +23154,19 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S18" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="T18" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="U18" s="3">
         <v>46296</v>
       </c>
       <c r="V18" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -26463,16 +26498,19 @@
         <v>176</v>
       </c>
       <c r="C158" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D158" t="s">
-        <v>347</v>
+        <v>346</v>
+      </c>
+      <c r="E158" t="s">
+        <v>9</v>
       </c>
       <c r="F158" t="s">
         <v>348</v>
       </c>
       <c r="G158" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="159" spans="1:7">

--- a/artifacts/BIST_Research_Latest.xlsx
+++ b/artifacts/BIST_Research_Latest.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7541" uniqueCount="532">
   <si>
     <t>Mode</t>
   </si>
@@ -1248,9 +1248,6 @@
     <t>kap_public</t>
   </si>
   <si>
-    <t>bist_official</t>
-  </si>
-  <si>
     <t>isyatirim_public</t>
   </si>
   <si>
@@ -1338,7 +1335,7 @@
     <t>KAP</t>
   </si>
   <si>
-    <t>Borsa Istanbul Daily Bulletin / DataStore</t>
+    <t>Borsa Istanbul Equity Market Daily Bulletin</t>
   </si>
   <si>
     <t>Official index constituent CSV</t>
@@ -1386,7 +1383,7 @@
     <t>https://www.kap.org.tr/</t>
   </si>
   <si>
-    <t>https://www.borsaistanbul.com/en/data/daily-bulletin</t>
+    <t>https://www.borsaistanbul.com/data/thb/</t>
   </si>
   <si>
     <t>https://www.borsaistanbul.com/datum/hisse_endeks_ds.csv</t>
@@ -1431,7 +1428,7 @@
     <t>financials_and_disclosures</t>
   </si>
   <si>
-    <t>exchange_reference</t>
+    <t>official_eod_price</t>
   </si>
   <si>
     <t>index_membership_reference</t>
@@ -1473,9 +1470,6 @@
     <t>partial</t>
   </si>
   <si>
-    <t>varies</t>
-  </si>
-  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -1485,7 +1479,7 @@
     <t>mixed</t>
   </si>
   <si>
-    <t>eod_or_licensed</t>
+    <t>eod</t>
   </si>
   <si>
     <t>reference</t>
@@ -1521,7 +1515,7 @@
     <t>['financial_statements', 'disclosures', 'corporate_actions', 'company_metadata']</t>
   </si>
   <si>
-    <t>['calendar', 'bulletins', 'corporate_actions', 'reference_data']</t>
+    <t>['trade_date', 'ticker', 'open', 'low', 'high', 'close', 'volume', 'turnover', 'session_close']</t>
   </si>
   <si>
     <t>['index_code', 'index_name', 'ticker', 'company_name']</t>
@@ -1560,7 +1554,7 @@
     <t>['fundamental_filters', 'technical_filters', 'custom_formulas', 'backtesting', 'strategy_models']</t>
   </si>
   <si>
-    <t>paid_or_datastore</t>
+    <t>daily_bulletin_archive</t>
   </si>
   <si>
     <t>unknown</t>
@@ -1578,6 +1572,9 @@
     <t>REVIEW_REQUIRED</t>
   </si>
   <si>
+    <t>PUBLIC_FILE_PATH_VALIDATED</t>
+  </si>
+  <si>
     <t>PUBLIC_REFERENCE_FILE</t>
   </si>
   <si>
@@ -1593,7 +1590,7 @@
     <t>PUBLIC_PAGES_ONLY</t>
   </si>
   <si>
-    <t>REALTIME_REDISTRIBUTION_LICENSE_REQUIRED</t>
+    <t>OFFICIAL_EOD_BULLETIN_USED_AS_PRICE_ANCHOR_NOT_REALTIME_REDISTRIBUTION</t>
   </si>
   <si>
     <t>REFERENCE_DATA_ONLY_NOT_REALTIME_REDISTRIBUTION</t>
@@ -22066,19 +22063,19 @@
         <v>392</v>
       </c>
       <c r="B2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -22087,10 +22084,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -22111,13 +22108,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="S2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="T2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="U2" s="3">
         <v>46296</v>
@@ -22131,19 +22128,19 @@
         <v>393</v>
       </c>
       <c r="B3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -22152,16 +22149,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -22176,13 +22173,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="T3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="U3" s="3">
         <v>46296</v>
@@ -22196,19 +22193,19 @@
         <v>394</v>
       </c>
       <c r="B4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -22217,10 +22214,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="K4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -22241,13 +22238,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="T4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="U4" s="3">
         <v>46296</v>
@@ -22258,37 +22255,37 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="B5" t="s">
         <v>366</v>
       </c>
       <c r="C5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E5" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F5" t="s">
-        <v>467</v>
-      </c>
-      <c r="G5" t="s">
-        <v>469</v>
-      </c>
-      <c r="H5" t="s">
-        <v>470</v>
+        <v>466</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M5" t="b">
         <v>0</v>
@@ -22306,10 +22303,10 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="S5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T5" t="s">
         <v>366</v>
@@ -22318,7 +22315,7 @@
         <v>46296</v>
       </c>
       <c r="V5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -22329,16 +22326,16 @@
         <v>366</v>
       </c>
       <c r="C6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -22347,10 +22344,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="K6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -22371,10 +22368,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T6" t="s">
         <v>366</v>
@@ -22388,22 +22385,22 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -22412,10 +22409,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -22436,19 +22433,19 @@
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="S7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="U7" s="3">
         <v>46296</v>
       </c>
       <c r="V7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -22456,19 +22453,19 @@
         <v>363</v>
       </c>
       <c r="B8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -22477,22 +22474,22 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K8" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P8" t="b">
         <v>0</v>
@@ -22501,10 +22498,10 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S8" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="T8" t="s">
         <v>368</v>
@@ -22518,22 +22515,22 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -22542,10 +22539,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K9" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -22566,36 +22563,36 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="U9" s="3">
         <v>46296</v>
       </c>
       <c r="V9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F10" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -22604,7 +22601,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K10" t="s">
         <v>350</v>
@@ -22628,51 +22625,51 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="U10" s="3">
         <v>46296</v>
       </c>
       <c r="V10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B11" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F11" t="s">
+        <v>467</v>
+      </c>
+      <c r="G11" t="s">
         <v>468</v>
-      </c>
-      <c r="G11" t="s">
-        <v>469</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -22684,69 +22681,69 @@
         <v>1</v>
       </c>
       <c r="O11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S11" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="T11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="U11" s="3">
         <v>46296</v>
       </c>
       <c r="V11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B12" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F12" t="s">
+        <v>467</v>
+      </c>
+      <c r="G12" t="s">
         <v>468</v>
-      </c>
-      <c r="G12" t="s">
-        <v>469</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -22761,39 +22758,39 @@
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S12" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="T12" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="U12" s="3">
         <v>46296</v>
       </c>
       <c r="V12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
@@ -22802,10 +22799,10 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -22814,51 +22811,51 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="O13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S13" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="U13" s="3">
         <v>46296</v>
       </c>
       <c r="V13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E14" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F14" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -22867,10 +22864,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K14" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -22879,51 +22876,51 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="O14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S14" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="U14" s="3">
         <v>46296</v>
       </c>
       <c r="V14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B15" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -22932,19 +22929,19 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -22953,175 +22950,175 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="U15" s="3">
         <v>46296</v>
       </c>
       <c r="V15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C16" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F16" t="s">
+        <v>467</v>
+      </c>
+      <c r="G16" t="s">
         <v>468</v>
-      </c>
-      <c r="G16" t="s">
-        <v>469</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K16" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="L16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
       <c r="O16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="T16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="U16" s="3">
         <v>46296</v>
       </c>
       <c r="V16" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B17" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C17" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F17" t="s">
+        <v>467</v>
+      </c>
+      <c r="G17" t="s">
         <v>468</v>
-      </c>
-      <c r="G17" t="s">
-        <v>469</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="K17" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="L17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="T17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="U17" s="3">
         <v>46296</v>
       </c>
       <c r="V17" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B18" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C18" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F18" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -23130,10 +23127,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K18" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -23154,19 +23151,19 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="S18" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="T18" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="U18" s="3">
         <v>46296</v>
       </c>
       <c r="V18" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/BIST_Research_Latest.xlsx
+++ b/artifacts/BIST_Research_Latest.xlsx
@@ -50,7 +50,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Quality Scanner'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'RSI Scanner'!$A$1:$H$325</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Source Status'!$A$1:$G$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">Sources!$A$1:$V$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">Sources!$A$1:$V$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'Target Prices'!$A$1:$A$325</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">Technical!$A$1:$C$325</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Value Scanner'!$A$1:$A$2</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7541" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7555" uniqueCount="543">
   <si>
     <t>Mode</t>
   </si>
@@ -93,10 +93,10 @@
     <t>2026-10-01</t>
   </si>
   <si>
-    <t>pending KAP adapter</t>
-  </si>
-  <si>
-    <t>pending discovery</t>
+    <t>SPK metadata/PDF only; structured KAP REST requires licensed access</t>
+  </si>
+  <si>
+    <t>terms-compatible discovery partial</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1248,6 +1248,9 @@
     <t>kap_public</t>
   </si>
   <si>
+    <t>kap_rest_api</t>
+  </si>
+  <si>
     <t>isyatirim_public</t>
   </si>
   <si>
@@ -1332,303 +1335,333 @@
     <t>TSPB Uye Bilgileri</t>
   </si>
   <si>
+    <t>KAP public pages</t>
+  </si>
+  <si>
+    <t>KAP Veri Yayin Servisi REST API</t>
+  </si>
+  <si>
+    <t>Borsa Istanbul Equity Market Daily Bulletin</t>
+  </si>
+  <si>
+    <t>Official index constituent CSV</t>
+  </si>
+  <si>
+    <t>Is Yatirim public analysis pages</t>
+  </si>
+  <si>
+    <t>Yahoo Finance</t>
+  </si>
+  <si>
+    <t>Investing.com public pages</t>
+  </si>
+  <si>
+    <t>ForInvest App / Web</t>
+  </si>
+  <si>
+    <t>Piapiri</t>
+  </si>
+  <si>
+    <t>MatriksIQ</t>
+  </si>
+  <si>
+    <t>iDeal</t>
+  </si>
+  <si>
+    <t>ZBorsa</t>
+  </si>
+  <si>
+    <t>TradeAll TR</t>
+  </si>
+  <si>
+    <t>Gedik Trader</t>
+  </si>
+  <si>
+    <t>QPS</t>
+  </si>
+  <si>
+    <t>https://ws.spk.gov.tr/help/index.html</t>
+  </si>
+  <si>
+    <t>https://tspb.org.tr/uye-bilgileri/</t>
+  </si>
+  <si>
+    <t>https://www.kap.org.tr/</t>
+  </si>
+  <si>
+    <t>https://www.borsaistanbul.com/data/thb/</t>
+  </si>
+  <si>
+    <t>https://www.borsaistanbul.com/datum/hisse_endeks_ds.csv</t>
+  </si>
+  <si>
+    <t>https://www.isyatirim.com.tr/tr-tr/analiz/hisse/Sayfalar/Tarihsel-Fiyat-Bilgileri.aspx</t>
+  </si>
+  <si>
+    <t>https://finance.yahoo.com/</t>
+  </si>
+  <si>
+    <t>https://www.investing.com/</t>
+  </si>
+  <si>
+    <t>https://www.forinvest.com/canli-veri</t>
+  </si>
+  <si>
+    <t>https://www.piapiri.com/</t>
+  </si>
+  <si>
+    <t>https://www.matriksdata.com/website/urunlerimiz/kullanici-platformlari/matriksiq-veri-terminali</t>
+  </si>
+  <si>
+    <t>https://www.idealdata.com.tr/</t>
+  </si>
+  <si>
+    <t>https://service.ziraatyatirim.com.tr/tr/zborsa</t>
+  </si>
+  <si>
+    <t>https://www.tradeall.com/</t>
+  </si>
+  <si>
+    <t>https://gedik.com/yatirimciya-ozel/gedik-trader</t>
+  </si>
+  <si>
+    <t>https://www.queenstocks.com/</t>
+  </si>
+  <si>
+    <t>registry</t>
+  </si>
+  <si>
+    <t>public_reference</t>
+  </si>
+  <si>
+    <t>licensed_structured_financials_and_disclosures</t>
+  </si>
+  <si>
+    <t>official_eod_price</t>
+  </si>
+  <si>
+    <t>index_membership_reference</t>
+  </si>
+  <si>
+    <t>price_financial_candidate</t>
+  </si>
+  <si>
+    <t>price_history</t>
+  </si>
+  <si>
+    <t>price_secondary</t>
+  </si>
+  <si>
+    <t>forbidden</t>
+  </si>
+  <si>
+    <t>market_data_and_research_candidate</t>
+  </si>
+  <si>
+    <t>market_data_research_model_portfolio_candidate</t>
+  </si>
+  <si>
+    <t>market_data_terminal_reference</t>
+  </si>
+  <si>
+    <t>broker_platform_reference</t>
+  </si>
+  <si>
+    <t>ux_strategy_reference_only</t>
+  </si>
+  <si>
+    <t>official</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>partial</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>periodic</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>contract_dependent</t>
+  </si>
+  <si>
+    <t>eod</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>delayed_or_page_dependent</t>
+  </si>
+  <si>
+    <t>delayed</t>
+  </si>
+  <si>
+    <t>live_for_free_membership</t>
+  </si>
+  <si>
+    <t>live_for_eligible_users</t>
+  </si>
+  <si>
+    <t>licensed</t>
+  </si>
+  <si>
+    <t>live_for_customers</t>
+  </si>
+  <si>
+    <t>account_dependent</t>
+  </si>
+  <si>
+    <t>['broker_list', 'bank_list', 'activity_permissions', 'listed_companies', 'financial_report_metadata', 'financial_report_pdf_document', 'special_disclosures']</t>
+  </si>
+  <si>
+    <t>['member_list', 'member_statistics']</t>
+  </si>
+  <si>
+    <t>['public_disclosure_pages', 'public_financial_pages', 'corporate_action_reference', 'company_metadata_reference']</t>
+  </si>
+  <si>
+    <t>['structured_financial_statements', 'disclosures', 'corporate_actions', 'company_metadata']</t>
+  </si>
+  <si>
+    <t>['trade_date', 'ticker', 'open', 'low', 'high', 'close', 'volume', 'turnover', 'session_close']</t>
+  </si>
+  <si>
+    <t>['index_code', 'index_name', 'ticker', 'company_name']</t>
+  </si>
+  <si>
+    <t>['historical_price', 'financial_statements', 'company_analysis']</t>
+  </si>
+  <si>
+    <t>['ohlcv', 'adjusted_close', 'dividends', 'splits']</t>
+  </si>
+  <si>
+    <t>['price', 'historical_ohlcv']</t>
+  </si>
+  <si>
+    <t>['prices', 'bist30', 'bist100', 'fundamentals', 'news', 'economic_calendar', 'research_reports']</t>
+  </si>
+  <si>
+    <t>['prices', 'watchlists', 'research_reports', 'model_portfolios', 'technical_signals']</t>
+  </si>
+  <si>
+    <t>['prices', 'technical_analysis', 'strategy_tools', 'trading']</t>
+  </si>
+  <si>
+    <t>['prices', 'technical_analysis', 'scanner', 'system_tester', 'custom_index']</t>
+  </si>
+  <si>
+    <t>['prices', 'research_reports', 'technical_analysis', 'recommendations', 'kap_news']</t>
+  </si>
+  <si>
+    <t>['prices', 'depth', 'charts', 'technical_analysis', 'news', 'reports']</t>
+  </si>
+  <si>
+    <t>['prices', 'watchlists', 'technical_analysis', 'news', 'trading']</t>
+  </si>
+  <si>
+    <t>['fundamental_filters', 'technical_filters', 'custom_formulas', 'backtesting', 'strategy_models']</t>
+  </si>
+  <si>
+    <t>daily_bulletin_archive</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>metadata_and_pdf_documents</t>
+  </si>
+  <si>
+    <t>aggregate</t>
+  </si>
+  <si>
+    <t>reference_only</t>
+  </si>
+  <si>
+    <t>limited</t>
+  </si>
+  <si>
+    <t>REVIEWED_PUBLIC_SERVICE</t>
+  </si>
+  <si>
+    <t>REVIEW_REQUIRED</t>
+  </si>
+  <si>
+    <t>REVIEWED_PUBLIC_REFERENCE</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>PUBLIC_FILE_PATH_VALIDATED</t>
+  </si>
+  <si>
+    <t>PUBLIC_REFERENCE_FILE</t>
+  </si>
+  <si>
+    <t>BLOCKED_PATH__LAYOUTS</t>
+  </si>
+  <si>
+    <t>PUBLIC_WEB_SERVICE</t>
+  </si>
+  <si>
+    <t>PUBLIC_DOWNLOADS</t>
+  </si>
+  <si>
+    <t>PUBLIC_REFERENCE_ONLY_NO_AUTOMATED_STORAGE_OR_HIGH_VOLUME_FETCH</t>
+  </si>
+  <si>
+    <t>BIST_DATA_DISTRIBUTION_AGREEMENT_MKK_AUTHORIZATION_AND_API_KEY_REQUIRED</t>
+  </si>
+  <si>
+    <t>OFFICIAL_EOD_BULLETIN_USED_AS_PRICE_ANCHOR_NOT_REALTIME_REDISTRIBUTION</t>
+  </si>
+  <si>
+    <t>REFERENCE_DATA_ONLY_NOT_REALTIME_REDISTRIBUTION</t>
+  </si>
+  <si>
+    <t>AUTOMATED_INGESTION_DISABLED_CONTENT_USE_RESTRICTED</t>
+  </si>
+  <si>
+    <t>UNDOCUMENTED_PUBLIC_ENDPOINT_USE_CAUTIOUSLY</t>
+  </si>
+  <si>
+    <t>AUTOMATED_FETCH_DISABLED_UNTIL_REVIEW</t>
+  </si>
+  <si>
+    <t>USER_FORBIDDEN</t>
+  </si>
+  <si>
+    <t>AUTOMATED_INGESTION_DISABLED_UNTIL_TERMS_REVIEW</t>
+  </si>
+  <si>
+    <t>PAID_PRODUCT_NOT_USED</t>
+  </si>
+  <si>
+    <t>CUSTOMER_LOGIN_REQUIRED_NO_AUTOMATED_INGESTION</t>
+  </si>
+  <si>
+    <t>LOGIN_REQUIRED_NO_AUTOMATED_INGESTION</t>
+  </si>
+  <si>
+    <t>REFERENCE_ONLY_NOT_INGESTED</t>
+  </si>
+  <si>
+    <t>SPK</t>
+  </si>
+  <si>
+    <t>TSPB</t>
+  </si>
+  <si>
     <t>KAP</t>
   </si>
   <si>
-    <t>Borsa Istanbul Equity Market Daily Bulletin</t>
-  </si>
-  <si>
-    <t>Official index constituent CSV</t>
-  </si>
-  <si>
-    <t>Is Yatirim public analysis pages</t>
-  </si>
-  <si>
-    <t>Yahoo Finance</t>
-  </si>
-  <si>
-    <t>Investing.com public pages</t>
-  </si>
-  <si>
-    <t>ForInvest App / Web</t>
-  </si>
-  <si>
-    <t>Piapiri</t>
-  </si>
-  <si>
-    <t>MatriksIQ</t>
-  </si>
-  <si>
-    <t>iDeal</t>
-  </si>
-  <si>
-    <t>ZBorsa</t>
-  </si>
-  <si>
-    <t>TradeAll TR</t>
-  </si>
-  <si>
-    <t>Gedik Trader</t>
-  </si>
-  <si>
-    <t>QPS</t>
-  </si>
-  <si>
-    <t>https://ws.spk.gov.tr/help/index.html</t>
-  </si>
-  <si>
-    <t>https://tspb.org.tr/uye-bilgileri/</t>
-  </si>
-  <si>
-    <t>https://www.kap.org.tr/</t>
-  </si>
-  <si>
-    <t>https://www.borsaistanbul.com/data/thb/</t>
-  </si>
-  <si>
-    <t>https://www.borsaistanbul.com/datum/hisse_endeks_ds.csv</t>
-  </si>
-  <si>
-    <t>https://www.isyatirim.com.tr/tr-tr/analiz/hisse/Sayfalar/Tarihsel-Fiyat-Bilgileri.aspx</t>
-  </si>
-  <si>
-    <t>https://finance.yahoo.com/</t>
-  </si>
-  <si>
-    <t>https://www.investing.com/</t>
-  </si>
-  <si>
-    <t>https://www.forinvest.com/canli-veri</t>
-  </si>
-  <si>
-    <t>https://www.piapiri.com/</t>
-  </si>
-  <si>
-    <t>https://www.matriksdata.com/website/urunlerimiz/kullanici-platformlari/matriksiq-veri-terminali</t>
-  </si>
-  <si>
-    <t>https://www.idealdata.com.tr/</t>
-  </si>
-  <si>
-    <t>https://service.ziraatyatirim.com.tr/tr/zborsa</t>
-  </si>
-  <si>
-    <t>https://www.tradeall.com/</t>
-  </si>
-  <si>
-    <t>https://gedik.com/yatirimciya-ozel/gedik-trader</t>
-  </si>
-  <si>
-    <t>https://www.queenstocks.com/</t>
-  </si>
-  <si>
-    <t>registry</t>
-  </si>
-  <si>
-    <t>financials_and_disclosures</t>
-  </si>
-  <si>
-    <t>official_eod_price</t>
-  </si>
-  <si>
-    <t>index_membership_reference</t>
-  </si>
-  <si>
-    <t>price_financial_candidate</t>
-  </si>
-  <si>
-    <t>price_history</t>
-  </si>
-  <si>
-    <t>price_secondary</t>
-  </si>
-  <si>
-    <t>forbidden</t>
-  </si>
-  <si>
-    <t>market_data_and_research_candidate</t>
-  </si>
-  <si>
-    <t>market_data_research_model_portfolio_candidate</t>
-  </si>
-  <si>
-    <t>market_data_terminal_reference</t>
-  </si>
-  <si>
-    <t>broker_platform_reference</t>
-  </si>
-  <si>
-    <t>ux_strategy_reference_only</t>
-  </si>
-  <si>
-    <t>official</t>
-  </si>
-  <si>
-    <t>secondary</t>
-  </si>
-  <si>
-    <t>partial</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>periodic</t>
-  </si>
-  <si>
-    <t>mixed</t>
-  </si>
-  <si>
-    <t>eod</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
-    <t>delayed_or_page_dependent</t>
-  </si>
-  <si>
-    <t>delayed</t>
-  </si>
-  <si>
-    <t>live_for_free_membership</t>
-  </si>
-  <si>
-    <t>live_for_eligible_users</t>
-  </si>
-  <si>
-    <t>licensed</t>
-  </si>
-  <si>
-    <t>live_for_customers</t>
-  </si>
-  <si>
-    <t>account_dependent</t>
-  </si>
-  <si>
-    <t>['broker_list', 'bank_list', 'activity_permissions', 'listed_companies', 'financial_report_metadata', 'special_disclosures']</t>
-  </si>
-  <si>
-    <t>['member_list', 'member_statistics']</t>
-  </si>
-  <si>
-    <t>['financial_statements', 'disclosures', 'corporate_actions', 'company_metadata']</t>
-  </si>
-  <si>
-    <t>['trade_date', 'ticker', 'open', 'low', 'high', 'close', 'volume', 'turnover', 'session_close']</t>
-  </si>
-  <si>
-    <t>['index_code', 'index_name', 'ticker', 'company_name']</t>
-  </si>
-  <si>
-    <t>['historical_price', 'financial_statements', 'company_analysis']</t>
-  </si>
-  <si>
-    <t>['ohlcv', 'adjusted_close', 'dividends', 'splits']</t>
-  </si>
-  <si>
-    <t>['price', 'historical_ohlcv']</t>
-  </si>
-  <si>
-    <t>['prices', 'bist30', 'bist100', 'fundamentals', 'news', 'economic_calendar', 'research_reports']</t>
-  </si>
-  <si>
-    <t>['prices', 'watchlists', 'research_reports', 'model_portfolios', 'technical_signals']</t>
-  </si>
-  <si>
-    <t>['prices', 'technical_analysis', 'strategy_tools', 'trading']</t>
-  </si>
-  <si>
-    <t>['prices', 'technical_analysis', 'scanner', 'system_tester', 'custom_index']</t>
-  </si>
-  <si>
-    <t>['prices', 'research_reports', 'technical_analysis', 'recommendations', 'kap_news']</t>
-  </si>
-  <si>
-    <t>['prices', 'depth', 'charts', 'technical_analysis', 'news', 'reports']</t>
-  </si>
-  <si>
-    <t>['prices', 'watchlists', 'technical_analysis', 'news', 'trading']</t>
-  </si>
-  <si>
-    <t>['fundamental_filters', 'technical_filters', 'custom_formulas', 'backtesting', 'strategy_models']</t>
-  </si>
-  <si>
-    <t>daily_bulletin_archive</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>aggregate</t>
-  </si>
-  <si>
-    <t>limited</t>
-  </si>
-  <si>
-    <t>REVIEWED_PUBLIC_SERVICE</t>
-  </si>
-  <si>
-    <t>REVIEW_REQUIRED</t>
-  </si>
-  <si>
-    <t>PUBLIC_FILE_PATH_VALIDATED</t>
-  </si>
-  <si>
-    <t>PUBLIC_REFERENCE_FILE</t>
-  </si>
-  <si>
-    <t>BLOCKED_PATH__LAYOUTS</t>
-  </si>
-  <si>
-    <t>PUBLIC_WEB_SERVICE</t>
-  </si>
-  <si>
-    <t>PUBLIC_DOWNLOADS</t>
-  </si>
-  <si>
-    <t>PUBLIC_PAGES_ONLY</t>
-  </si>
-  <si>
-    <t>OFFICIAL_EOD_BULLETIN_USED_AS_PRICE_ANCHOR_NOT_REALTIME_REDISTRIBUTION</t>
-  </si>
-  <si>
-    <t>REFERENCE_DATA_ONLY_NOT_REALTIME_REDISTRIBUTION</t>
-  </si>
-  <si>
-    <t>AUTOMATED_INGESTION_DISABLED_CONTENT_USE_RESTRICTED</t>
-  </si>
-  <si>
-    <t>UNDOCUMENTED_PUBLIC_ENDPOINT_USE_CAUTIOUSLY</t>
-  </si>
-  <si>
-    <t>AUTOMATED_FETCH_DISABLED_UNTIL_REVIEW</t>
-  </si>
-  <si>
-    <t>USER_FORBIDDEN</t>
-  </si>
-  <si>
-    <t>AUTOMATED_INGESTION_DISABLED_UNTIL_TERMS_REVIEW</t>
-  </si>
-  <si>
-    <t>PAID_PRODUCT_NOT_USED</t>
-  </si>
-  <si>
-    <t>CUSTOMER_LOGIN_REQUIRED_NO_AUTOMATED_INGESTION</t>
-  </si>
-  <si>
-    <t>LOGIN_REQUIRED_NO_AUTOMATED_INGESTION</t>
-  </si>
-  <si>
-    <t>REFERENCE_ONLY_NOT_INGESTED</t>
-  </si>
-  <si>
-    <t>SPK</t>
-  </si>
-  <si>
-    <t>TSPB</t>
-  </si>
-  <si>
     <t>Matriks_on_historical_price_page</t>
   </si>
   <si>
@@ -1647,13 +1680,13 @@
     <t>Foreks_or_other_vendor_unverified</t>
   </si>
   <si>
+    <t>DISABLED</t>
+  </si>
+  <si>
+    <t>PAID_SOURCE_SKIPPED</t>
+  </si>
+  <si>
     <t>BLOCKED</t>
-  </si>
-  <si>
-    <t>DISABLED</t>
-  </si>
-  <si>
-    <t>PAID_SOURCE_SKIPPED</t>
   </si>
   <si>
     <t>LOGIN_REQUIRED</t>
@@ -21964,7 +21997,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="13.7109375" customWidth="1"/>
@@ -22063,19 +22096,19 @@
         <v>392</v>
       </c>
       <c r="B2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -22084,16 +22117,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="K2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
-      <c r="M2" t="b">
-        <v>1</v>
+      <c r="M2" t="s">
+        <v>504</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -22108,13 +22141,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="S2" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="T2" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="U2" s="3">
         <v>46296</v>
@@ -22128,19 +22161,19 @@
         <v>393</v>
       </c>
       <c r="B3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F3" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -22149,16 +22182,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="K3" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -22173,13 +22206,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="S3" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="T3" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
       <c r="U3" s="3">
         <v>46296</v>
@@ -22193,19 +22226,19 @@
         <v>394</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F4" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -22214,16 +22247,16 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
       </c>
-      <c r="M4" t="b">
-        <v>1</v>
+      <c r="M4" t="s">
+        <v>506</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -22238,57 +22271,57 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="S4" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="T4" t="s">
-        <v>423</v>
+        <v>532</v>
       </c>
       <c r="U4" s="3">
         <v>46296</v>
       </c>
       <c r="V4" t="s">
-        <v>364</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="B5" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="C5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
       <c r="I5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K5" t="s">
-        <v>484</v>
-      </c>
-      <c r="L5" t="s">
-        <v>497</v>
+        <v>488</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
       </c>
       <c r="M5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -22300,42 +22333,42 @@
         <v>0</v>
       </c>
       <c r="Q5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="S5" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="T5" t="s">
-        <v>366</v>
+        <v>532</v>
       </c>
       <c r="U5" s="3">
         <v>46296</v>
       </c>
       <c r="V5" t="s">
-        <v>364</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B6" t="s">
         <v>366</v>
       </c>
       <c r="C6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F6" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -22344,13 +22377,13 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="K6" t="s">
-        <v>485</v>
-      </c>
-      <c r="L6" t="b">
-        <v>0</v>
+        <v>489</v>
+      </c>
+      <c r="L6" t="s">
+        <v>502</v>
       </c>
       <c r="M6" t="b">
         <v>0</v>
@@ -22368,10 +22401,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="S6" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="T6" t="s">
         <v>366</v>
@@ -22385,22 +22418,22 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="B7" t="s">
-        <v>409</v>
+        <v>366</v>
       </c>
       <c r="C7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -22409,63 +22442,63 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="K7" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="L7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="S7" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="T7" t="s">
-        <v>522</v>
+        <v>366</v>
       </c>
       <c r="U7" s="3">
         <v>46296</v>
       </c>
       <c r="V7" t="s">
-        <v>528</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="B8" t="s">
         <v>410</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -22474,63 +22507,63 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K8" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
       </c>
-      <c r="M8" t="s">
-        <v>500</v>
+      <c r="M8" t="b">
+        <v>1</v>
       </c>
       <c r="N8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>500</v>
+        <v>1</v>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
       </c>
       <c r="P8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="S8" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="T8" t="s">
-        <v>368</v>
+        <v>533</v>
       </c>
       <c r="U8" s="3">
         <v>46296</v>
       </c>
       <c r="V8" t="s">
-        <v>364</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="B9" t="s">
         <v>411</v>
       </c>
       <c r="C9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E9" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F9" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -22539,22 +22572,22 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="K9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
-      <c r="M9" t="b">
-        <v>1</v>
+      <c r="M9" t="s">
+        <v>507</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="b">
-        <v>1</v>
+      <c r="O9" t="s">
+        <v>507</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
@@ -22563,19 +22596,19 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="S9" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="T9" t="s">
-        <v>523</v>
+        <v>368</v>
       </c>
       <c r="U9" s="3">
         <v>46296</v>
       </c>
       <c r="V9" t="s">
-        <v>529</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -22586,55 +22619,61 @@
         <v>412</v>
       </c>
       <c r="C10" t="s">
-        <v>412</v>
+        <v>430</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="E10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F10" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="H10" t="b">
+      <c r="I10" t="s">
+        <v>479</v>
+      </c>
+      <c r="K10" t="s">
+        <v>493</v>
+      </c>
+      <c r="L10" t="b">
         <v>1</v>
       </c>
-      <c r="I10" t="s">
-        <v>469</v>
-      </c>
-      <c r="K10" t="s">
-        <v>350</v>
-      </c>
-      <c r="L10" t="b">
-        <v>0</v>
-      </c>
       <c r="M10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="b">
         <v>0</v>
       </c>
       <c r="Q10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="S10" t="s">
-        <v>514</v>
+        <v>523</v>
+      </c>
+      <c r="T10" t="s">
+        <v>534</v>
       </c>
       <c r="U10" s="3">
         <v>46296</v>
       </c>
       <c r="V10" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -22645,64 +22684,55 @@
         <v>413</v>
       </c>
       <c r="C11" t="s">
-        <v>429</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>445</v>
+        <v>413</v>
       </c>
       <c r="E11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F11" t="s">
-        <v>467</v>
-      </c>
-      <c r="G11" t="s">
-        <v>468</v>
+        <v>470</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>476</v>
-      </c>
-      <c r="J11">
+        <v>472</v>
+      </c>
+      <c r="K11" t="s">
+        <v>350</v>
+      </c>
+      <c r="L11" t="b">
         <v>0</v>
       </c>
-      <c r="K11" t="s">
-        <v>489</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
       <c r="M11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="b">
-        <v>1</v>
-      </c>
-      <c r="O11" t="s">
-        <v>498</v>
-      </c>
-      <c r="P11" t="s">
-        <v>498</v>
+        <v>0</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
       </c>
       <c r="Q11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="S11" t="s">
-        <v>515</v>
-      </c>
-      <c r="T11" t="s">
         <v>524</v>
       </c>
       <c r="U11" s="3">
         <v>46296</v>
       </c>
       <c r="V11" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -22713,64 +22743,64 @@
         <v>414</v>
       </c>
       <c r="C12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E12" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="F12" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G12" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>490</v>
-      </c>
-      <c r="L12" t="s">
-        <v>498</v>
-      </c>
-      <c r="M12" t="s">
-        <v>498</v>
+        <v>494</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
       </c>
-      <c r="O12" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" t="b">
-        <v>1</v>
+      <c r="O12" t="s">
+        <v>503</v>
+      </c>
+      <c r="P12" t="s">
+        <v>503</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="S12" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="T12" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="U12" s="3">
         <v>46296</v>
       </c>
       <c r="V12" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -22781,61 +22811,64 @@
         <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E13" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F13" t="s">
-        <v>467</v>
-      </c>
-      <c r="G13" t="b">
-        <v>0</v>
+        <v>470</v>
+      </c>
+      <c r="G13" t="s">
+        <v>471</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>478</v>
+        <v>481</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>491</v>
-      </c>
-      <c r="L13" t="b">
+        <v>495</v>
+      </c>
+      <c r="L13" t="s">
+        <v>503</v>
+      </c>
+      <c r="M13" t="s">
+        <v>503</v>
+      </c>
+      <c r="N13" t="b">
         <v>1</v>
       </c>
-      <c r="M13" t="b">
+      <c r="O13" t="b">
         <v>1</v>
       </c>
-      <c r="N13" t="s">
-        <v>498</v>
-      </c>
-      <c r="O13" t="s">
-        <v>498</v>
-      </c>
-      <c r="P13" t="s">
-        <v>498</v>
+      <c r="P13" t="b">
+        <v>1</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="S13" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="T13" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="U13" s="3">
         <v>46296</v>
       </c>
       <c r="V13" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -22846,16 +22879,16 @@
         <v>416</v>
       </c>
       <c r="C14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E14" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F14" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G14" t="b">
         <v>0</v>
@@ -22864,10 +22897,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="K14" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -22876,31 +22909,31 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="O14" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="P14" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="S14" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="T14" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="U14" s="3">
         <v>46296</v>
       </c>
       <c r="V14" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -22911,64 +22944,61 @@
         <v>417</v>
       </c>
       <c r="C15" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F15" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>479</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="K15" t="s">
-        <v>493</v>
-      </c>
-      <c r="L15" t="s">
-        <v>498</v>
-      </c>
-      <c r="M15" t="s">
-        <v>498</v>
-      </c>
-      <c r="N15" t="b">
+        <v>497</v>
+      </c>
+      <c r="L15" t="b">
         <v>1</v>
       </c>
-      <c r="O15" t="b">
+      <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="s">
+        <v>503</v>
+      </c>
+      <c r="O15" t="s">
+        <v>503</v>
+      </c>
       <c r="P15" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="S15" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="T15" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="U15" s="3">
         <v>46296</v>
       </c>
       <c r="V15" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -22979,61 +23009,64 @@
         <v>418</v>
       </c>
       <c r="C16" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E16" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F16" t="s">
-        <v>467</v>
-      </c>
-      <c r="G16" t="s">
-        <v>468</v>
+        <v>470</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>480</v>
+        <v>483</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="L16" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M16" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
       </c>
-      <c r="O16" t="s">
-        <v>498</v>
+      <c r="O16" t="b">
+        <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>502</v>
+        <v>472</v>
       </c>
       <c r="S16" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="T16" t="s">
-        <v>498</v>
+        <v>538</v>
       </c>
       <c r="U16" s="3">
         <v>46296</v>
       </c>
       <c r="V16" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -23044,61 +23077,61 @@
         <v>419</v>
       </c>
       <c r="C17" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E17" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="F17" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="G17" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="K17" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L17" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="M17" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
       </c>
       <c r="O17" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="P17" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="S17" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="T17" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="U17" s="3">
         <v>46296</v>
       </c>
       <c r="V17" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -23109,65 +23142,130 @@
         <v>420</v>
       </c>
       <c r="C18" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E18" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F18" t="s">
-        <v>467</v>
-      </c>
-      <c r="G18" t="b">
-        <v>0</v>
+        <v>470</v>
+      </c>
+      <c r="G18" t="s">
+        <v>471</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="K18" t="s">
-        <v>496</v>
-      </c>
-      <c r="L18" t="b">
+        <v>500</v>
+      </c>
+      <c r="L18" t="s">
+        <v>503</v>
+      </c>
+      <c r="M18" t="s">
+        <v>503</v>
+      </c>
+      <c r="N18" t="b">
         <v>1</v>
       </c>
-      <c r="M18" t="b">
+      <c r="O18" t="s">
+        <v>503</v>
+      </c>
+      <c r="P18" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q18" t="b">
         <v>1</v>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18" t="b">
-        <v>0</v>
-      </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
       <c r="R18" t="s">
-        <v>469</v>
+        <v>509</v>
       </c>
       <c r="S18" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="T18" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="U18" s="3">
         <v>46296</v>
       </c>
       <c r="V18" t="s">
-        <v>530</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19" t="s">
+        <v>406</v>
+      </c>
+      <c r="B19" t="s">
+        <v>421</v>
+      </c>
+      <c r="C19" t="s">
+        <v>438</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E19" t="s">
+        <v>468</v>
+      </c>
+      <c r="F19" t="s">
+        <v>470</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>472</v>
+      </c>
+      <c r="K19" t="s">
+        <v>501</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>472</v>
+      </c>
+      <c r="S19" t="s">
+        <v>529</v>
+      </c>
+      <c r="T19" t="s">
+        <v>503</v>
+      </c>
+      <c r="U19" s="3">
+        <v>46296</v>
+      </c>
+      <c r="V19" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V18"/>
+  <autoFilter ref="A1:V19"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1"/>
     <hyperlink ref="D3" r:id="rId2"/>
@@ -23177,7 +23275,7 @@
     <hyperlink ref="D7" r:id="rId6"/>
     <hyperlink ref="D8" r:id="rId7"/>
     <hyperlink ref="D9" r:id="rId8"/>
-    <hyperlink ref="D11" r:id="rId9"/>
+    <hyperlink ref="D10" r:id="rId9"/>
     <hyperlink ref="D12" r:id="rId10"/>
     <hyperlink ref="D13" r:id="rId11"/>
     <hyperlink ref="D14" r:id="rId12"/>
@@ -23185,6 +23283,7 @@
     <hyperlink ref="D16" r:id="rId14"/>
     <hyperlink ref="D17" r:id="rId15"/>
     <hyperlink ref="D18" r:id="rId16"/>
+    <hyperlink ref="D19" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
